--- a/List guidelines/Annex1SustainabilityOntologyLIstGuidelines.xlsx
+++ b/List guidelines/Annex1SustainabilityOntologyLIstGuidelines.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaubb\Desktop\The-List-of-Sustainability-Ontologies\List guidelines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/The-List-of-Sustainability-Ontologies/List guidelines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B83129F-9118-4262-9B4B-A74F5FB8EF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3359B4-844C-D342-9858-BAF0F74DB129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0EE024C9-D693-431A-88E6-73D80E12ECFE}"/>
+    <workbookView xWindow="33780" yWindow="1320" windowWidth="28540" windowHeight="19180" xr2:uid="{0EE024C9-D693-431A-88E6-73D80E12ECFE}"/>
   </bookViews>
   <sheets>
     <sheet name="ListGuidelines" sheetId="2" r:id="rId1"/>
@@ -82,12 +82,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Path 1:  Our review assessment started from papers retrieved using the keywords “Sustainability”, “Sustainable development” and “Ontology”. We complemented this pool of initial papers with those gathered using the other keywords listed in Table 1. We analyzed all ontologies presented in the collected papers. If an ontology was found to be primarily relevant to the themes characterizing the sustainability debate that we addressed in Section 1, we further assessed additional related literature, ontology files, and repositories (if available).                                                                                                          
-                                                                                                                                                                                                                                                                                                                                                                             The review assessment primarily relied on papers that were either review papers or research papers that also contained a section (usually an introductory one) dedicated to reviewing existing and related ontologies. Thus, to avoid a snowball effect resulting in an unmanageable number of ontologies to assess, we generally limited our analysis to the info presented in gathered papers without investigating the additional literature reviewed by those papers (except those few resources that appeared fundamental, for which we conducted a further analysis exploring additional related literature). 
-                                                                                                                                                                                                                                                                                                                                                                      Some of the ontologies we examined did not present any ontology files or repositories. These resources may not have been released online or simply they were not available to the public. 
-                                                                                                                                                                                                                                                                                                                                                                           List A documents all the main ontologies assessed in this path. Few ontologies were excluded as slightly significant in terms of the themes characterizing the sustainability debate. An exception to that is those presented by  Baydaroğlu et al. (2023) who reviewed currently available ontologies in the hydrogeology domain. Due to the large number of covered resources and the limited information presented for each of them, in this case, we decided to include only those authors indicated as the most relevant ones. For learning about other hydrogeology ontologies, we refer readers directly to the publication of Baydaroğlu et al. (2023). In this list, we included the major top-level ontologies mentioned in the analyzed papers.                  </t>
-  </si>
-  <si>
     <r>
       <t>Path 2:</t>
     </r>
@@ -140,6 +134,12 @@
       <t xml:space="preserve"> For all the ontologies included in the list, we provided references to main related publications or webpages presenting connected documentation. For a few resources, we were not able to identify any reference documents. In those cases (indicated with an * in the  List A “Ontology Name” column), we provided links to homepages or repositories. If we identified neither a homepage nor a repository, we furnish the link to the portal page where we retrieved them.
                                                                                                                                                                                                                                                                                                                                                                                           For ontologies gathered through Path 1, we provided links to papers we analyzed and to those cited in the related bibliographies. References to ontologies collected through Path 2 were chosen according to the documentation specified in the portals where we identified these resources. If no publications were available, we explored ontology repositories or homepages. We also queried for ontology names, author names, and essential keywords, such as the names of the projects within which the ontologies were developed, in Google Scholar and PubMed search engines. The exploration was expanded to Google browser at times, to increase the chance of identifying the related documentation.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Path 1:  Our review assessment started from papers retrieved using the keywords “Sustainability”, “Sustainable development” and “Ontology”. We complemented this pool of initial papers with those gathered using the other keywords listed in Table 1. We analyzed all ontologies presented in the collected papers. If an ontology was found to be primarily relevant to the themes characterizing the sustainability debate that we addressed in Section 1, we further assessed additional related literature, ontology files, and repositories (if available).                                                                                                          
+                                                                                                                                                                                                                                                                                                                                                                             The review assessment primarily relied on papers that were either review papers or research papers that also contained a section (usually an introductory one) dedicated to reviewing existing and related ontologies. Thus, to avoid a snowball effect resulting in an unmanageable number of ontologies to assess, we generally limited our analysis to the info presented in gathered papers without investigating the additional literature reviewed by those papers (except those few resources that appeared fundamental, for which we conducted a further analysis exploring additional related literature). 
+                                                                                                                                                                                                                                                                                                                                                                      Some of the ontologies we examined did not present any ontology files or repositories. These resources may not have been released online or simply they were not available to the public. 
+                                                                                                                                                                                                                                                                                                                                                                           List A documents all the main ontologies assessed in this path. Few ontologies were excluded as slightly significant in terms of the themes characterizing the sustainability debate. An exception to that is those presented by  Baydaroğlu et al. (2023) who reviewed currently available ontologies in the hydrogeology domain. Due to the large number of covered resources and the limited information presented for each of them, in this case, we decided to include only those authors indicated as the most relevant ones. For learning about other hydrogeology ontologies, we refer readers directly to the publication of Baydaroğlu et al. (2023). In this list, we included the major top-level ontologies mentioned in the analyzed papers.                                                                                                            Baydaroğlu Ö, Yeşilköy S, Sermet Y, Demir I (2023) A comprehensive review of ontologies in the hydrology towards guiding next generation artificial intelligence applications. Journal of Environmental Informatics. https://doi.org/10.3808/jei.202300500               </t>
   </si>
 </sst>
 </file>
@@ -484,7 +484,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Normale 2" xfId="1" xr:uid="{DA642D50-3BB0-4E4A-B532-9EAD7A743246}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -501,7 +501,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -798,9 +798,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8072C8F5-7651-4A76-996F-BDC420456278}">
   <dimension ref="A1:S71"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -822,7 +822,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -842,7 +842,7 @@
       <c r="Q2" s="12"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -864,7 +864,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
@@ -886,7 +886,7 @@
       <c r="Q4" s="20"/>
       <c r="R4" s="21"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="22"/>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -906,7 +906,7 @@
       <c r="Q5" s="23"/>
       <c r="R5" s="24"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -926,7 +926,7 @@
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -946,7 +946,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
@@ -968,7 +968,7 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="10"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -988,7 +988,7 @@
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>1</v>
       </c>
@@ -1010,7 +1010,7 @@
       <c r="Q10" s="16"/>
       <c r="R10" s="17"/>
     </row>
-    <row r="11" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="39" t="s">
         <v>7</v>
       </c>
@@ -1032,7 +1032,7 @@
       <c r="Q11" s="40"/>
       <c r="R11" s="41"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
@@ -1052,7 +1052,7 @@
       <c r="Q12" s="43"/>
       <c r="R12" s="44"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
@@ -1072,7 +1072,7 @@
       <c r="Q13" s="43"/>
       <c r="R13" s="44"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
@@ -1092,7 +1092,7 @@
       <c r="Q14" s="43"/>
       <c r="R14" s="44"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="45"/>
       <c r="B15" s="46"/>
       <c r="C15" s="46"/>
@@ -1112,7 +1112,7 @@
       <c r="Q15" s="46"/>
       <c r="R15" s="47"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="48"/>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
@@ -1132,7 +1132,7 @@
       <c r="Q16" s="48"/>
       <c r="R16" s="48"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>5</v>
       </c>
@@ -1154,7 +1154,7 @@
       <c r="Q17" s="16"/>
       <c r="R17" s="17"/>
     </row>
-    <row r="18" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="30" t="s">
         <v>8</v>
       </c>
@@ -1176,7 +1176,7 @@
       <c r="Q18" s="31"/>
       <c r="R18" s="32"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="33"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -1196,7 +1196,7 @@
       <c r="Q19" s="34"/>
       <c r="R19" s="35"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="33"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -1216,7 +1216,7 @@
       <c r="Q20" s="34"/>
       <c r="R20" s="35"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="33"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -1236,7 +1236,7 @@
       <c r="Q21" s="34"/>
       <c r="R21" s="35"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="36"/>
       <c r="B22" s="37"/>
       <c r="C22" s="37"/>
@@ -1256,7 +1256,7 @@
       <c r="Q22" s="37"/>
       <c r="R22" s="38"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="25"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -1276,7 +1276,7 @@
       <c r="Q23" s="25"/>
       <c r="R23" s="25"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
         <v>2</v>
       </c>
@@ -1298,9 +1298,9 @@
       <c r="Q24" s="16"/>
       <c r="R24" s="17"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -1320,7 +1320,7 @@
       <c r="Q25" s="18"/>
       <c r="R25" s="27"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="28"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1340,9 +1340,9 @@
       <c r="Q26" s="7"/>
       <c r="R26" s="29"/>
     </row>
-    <row r="27" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
@@ -1362,7 +1362,7 @@
       <c r="Q27" s="31"/>
       <c r="R27" s="32"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="33"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -1382,7 +1382,7 @@
       <c r="Q28" s="34"/>
       <c r="R28" s="35"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="33"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -1402,7 +1402,7 @@
       <c r="Q29" s="34"/>
       <c r="R29" s="35"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="33"/>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
@@ -1422,7 +1422,7 @@
       <c r="Q30" s="34"/>
       <c r="R30" s="35"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="33"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -1442,7 +1442,7 @@
       <c r="Q31" s="34"/>
       <c r="R31" s="35"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="33"/>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
@@ -1462,7 +1462,7 @@
       <c r="Q32" s="34"/>
       <c r="R32" s="35"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="33"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -1482,7 +1482,7 @@
       <c r="Q33" s="34"/>
       <c r="R33" s="35"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="33"/>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -1502,7 +1502,7 @@
       <c r="Q34" s="34"/>
       <c r="R34" s="35"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="33"/>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -1522,7 +1522,7 @@
       <c r="Q35" s="34"/>
       <c r="R35" s="35"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="33"/>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -1542,7 +1542,7 @@
       <c r="Q36" s="34"/>
       <c r="R36" s="35"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="33"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -1562,7 +1562,7 @@
       <c r="Q37" s="34"/>
       <c r="R37" s="35"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="33"/>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -1585,7 +1585,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="33"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -1605,7 +1605,7 @@
       <c r="Q39" s="34"/>
       <c r="R39" s="35"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="33"/>
       <c r="B40" s="34"/>
       <c r="C40" s="34"/>
@@ -1625,7 +1625,7 @@
       <c r="Q40" s="34"/>
       <c r="R40" s="35"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="36"/>
       <c r="B41" s="37"/>
       <c r="C41" s="37"/>
@@ -1645,9 +1645,9 @@
       <c r="Q41" s="37"/>
       <c r="R41" s="38"/>
     </row>
-    <row r="42" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -1667,7 +1667,7 @@
       <c r="Q42" s="40"/>
       <c r="R42" s="41"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="42"/>
       <c r="B43" s="43"/>
       <c r="C43" s="43"/>
@@ -1687,7 +1687,7 @@
       <c r="Q43" s="43"/>
       <c r="R43" s="44"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="42"/>
       <c r="B44" s="43"/>
       <c r="C44" s="43"/>
@@ -1707,7 +1707,7 @@
       <c r="Q44" s="43"/>
       <c r="R44" s="44"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="42"/>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -1727,7 +1727,7 @@
       <c r="Q45" s="43"/>
       <c r="R45" s="44"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="42"/>
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
@@ -1747,7 +1747,7 @@
       <c r="Q46" s="43"/>
       <c r="R46" s="44"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="42"/>
       <c r="B47" s="43"/>
       <c r="C47" s="43"/>
@@ -1767,7 +1767,7 @@
       <c r="Q47" s="43"/>
       <c r="R47" s="44"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="42"/>
       <c r="B48" s="43"/>
       <c r="C48" s="43"/>
@@ -1787,7 +1787,7 @@
       <c r="Q48" s="43"/>
       <c r="R48" s="44"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="42"/>
       <c r="B49" s="43"/>
       <c r="C49" s="43"/>
@@ -1807,7 +1807,7 @@
       <c r="Q49" s="43"/>
       <c r="R49" s="44"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="42"/>
       <c r="B50" s="43"/>
       <c r="C50" s="43"/>
@@ -1827,7 +1827,7 @@
       <c r="Q50" s="43"/>
       <c r="R50" s="44"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="45"/>
       <c r="B51" s="46"/>
       <c r="C51" s="46"/>
@@ -1847,9 +1847,9 @@
       <c r="Q51" s="46"/>
       <c r="R51" s="47"/>
     </row>
-    <row r="52" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
@@ -1869,7 +1869,7 @@
       <c r="Q52" s="31"/>
       <c r="R52" s="32"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="33"/>
       <c r="B53" s="34"/>
       <c r="C53" s="34"/>
@@ -1889,7 +1889,7 @@
       <c r="Q53" s="34"/>
       <c r="R53" s="35"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="33"/>
       <c r="B54" s="34"/>
       <c r="C54" s="34"/>
@@ -1909,7 +1909,7 @@
       <c r="Q54" s="34"/>
       <c r="R54" s="35"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="33"/>
       <c r="B55" s="34"/>
       <c r="C55" s="34"/>
@@ -1929,7 +1929,7 @@
       <c r="Q55" s="34"/>
       <c r="R55" s="35"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="33"/>
       <c r="B56" s="34"/>
       <c r="C56" s="34"/>
@@ -1949,7 +1949,7 @@
       <c r="Q56" s="34"/>
       <c r="R56" s="35"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="33"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -1969,7 +1969,7 @@
       <c r="Q57" s="34"/>
       <c r="R57" s="35"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="33"/>
       <c r="B58" s="34"/>
       <c r="C58" s="34"/>
@@ -1989,7 +1989,7 @@
       <c r="Q58" s="34"/>
       <c r="R58" s="35"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="33"/>
       <c r="B59" s="34"/>
       <c r="C59" s="34"/>
@@ -2009,7 +2009,7 @@
       <c r="Q59" s="34"/>
       <c r="R59" s="35"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="33"/>
       <c r="B60" s="34"/>
       <c r="C60" s="34"/>
@@ -2029,7 +2029,7 @@
       <c r="Q60" s="34"/>
       <c r="R60" s="35"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="36"/>
       <c r="B61" s="37"/>
       <c r="C61" s="37"/>
@@ -2049,7 +2049,7 @@
       <c r="Q61" s="37"/>
       <c r="R61" s="38"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -2069,7 +2069,7 @@
       <c r="Q62" s="12"/>
       <c r="R62" s="12"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="15" t="s">
         <v>9</v>
       </c>
@@ -2091,7 +2091,7 @@
       <c r="Q63" s="16"/>
       <c r="R63" s="17"/>
     </row>
-    <row r="64" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="49" t="s">
         <v>10</v>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="Q64" s="49"/>
       <c r="R64" s="49"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="49"/>
       <c r="B65" s="49"/>
       <c r="C65" s="49"/>
@@ -2133,7 +2133,7 @@
       <c r="Q65" s="49"/>
       <c r="R65" s="49"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="49"/>
       <c r="B66" s="49"/>
       <c r="C66" s="49"/>
@@ -2153,7 +2153,7 @@
       <c r="Q66" s="49"/>
       <c r="R66" s="49"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="49"/>
       <c r="B67" s="49"/>
       <c r="C67" s="49"/>
@@ -2173,7 +2173,7 @@
       <c r="Q67" s="49"/>
       <c r="R67" s="49"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="49"/>
       <c r="B68" s="49"/>
       <c r="C68" s="49"/>
@@ -2193,7 +2193,7 @@
       <c r="Q68" s="49"/>
       <c r="R68" s="49"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="49"/>
       <c r="B69" s="49"/>
       <c r="C69" s="49"/>
@@ -2213,7 +2213,7 @@
       <c r="Q69" s="49"/>
       <c r="R69" s="49"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="49"/>
       <c r="B70" s="49"/>
       <c r="C70" s="49"/>
@@ -2233,7 +2233,7 @@
       <c r="Q70" s="49"/>
       <c r="R70" s="49"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" s="49"/>
       <c r="B71" s="49"/>
       <c r="C71" s="49"/>
